--- a/data/trans_camb/P1426-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1426-Habitat-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,2</t>
+          <t>3,94</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,16</t>
+          <t>4,06</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,18</t>
+          <t>4,0</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,84</t>
+          <t>-2,27; 0,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,14</t>
+          <t>1,92; 5,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,24</t>
+          <t>-1,96; 1,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,78</t>
+          <t>2,19; 5,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,46</t>
+          <t>-1,64; 0,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,33</t>
+          <t>2,71; 5,19</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>187,89%</t>
+          <t>176,49%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>206,57%</t>
+          <t>201,61%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>196,49%</t>
+          <t>188,26%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-69,13; 74,1</t>
+          <t>-72,09; 60,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,51; 446,67</t>
+          <t>55,82; 448,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-63,37; 120,21</t>
+          <t>-67,16; 88,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,95; 485,18</t>
+          <t>66,94; 460,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,54; 29,61</t>
+          <t>-59,93; 29,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,51; 337,09</t>
+          <t>89,74; 332,54</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>3,48</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>2,85</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>3,16</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,65</t>
+          <t>-1,25; 0,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,23</t>
+          <t>2,13; 4,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,08</t>
+          <t>-0,54; 2,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,45</t>
+          <t>1,63; 4,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,01</t>
+          <t>-0,6; 1,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,9</t>
+          <t>2,29; 4,1</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>202,79%</t>
+          <t>261,11%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>181,97%</t>
+          <t>166,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>188,1%</t>
+          <t>207,96%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,61; 98,78</t>
+          <t>-69,87; 96,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,5; 507,93</t>
+          <t>95,97; 639,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 192,1</t>
+          <t>-26,77; 173,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72,26; 405,93</t>
+          <t>59,95; 356,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,7; 88,63</t>
+          <t>-32,25; 95,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,35; 332,5</t>
+          <t>110,9; 357,88</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>2,65</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2,12</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>2,38</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,37</t>
+          <t>-0,78; 1,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,02</t>
+          <t>1,19; 4,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,52</t>
+          <t>-1,33; 1,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,86</t>
+          <t>0,42; 3,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,21</t>
+          <t>-0,63; 1,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,01</t>
+          <t>1,31; 3,45</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>259,85%</t>
+          <t>275,93%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>117,29%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>130,47%</t>
+          <t>171,35%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,18; 344,92</t>
+          <t>-61,36; 302,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,78; 868,42</t>
+          <t>56,78; 995,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,37; 155,14</t>
+          <t>-55,25; 159,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,61; 268,49</t>
+          <t>11,78; 361,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,68; 136,33</t>
+          <t>-35,22; 115,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,84; 323,81</t>
+          <t>61,31; 347,78</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>2,52</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,5</t>
+          <t>-0,98; 1,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,11</t>
+          <t>1,05; 4,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,23</t>
+          <t>-1,15; 1,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,41</t>
+          <t>1,26; 3,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,04</t>
+          <t>-0,76; 0,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,38</t>
+          <t>1,58; 3,48</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>157,78%</t>
+          <t>148,43%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>112,57%</t>
+          <t>130,28%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>132,44%</t>
+          <t>138,4%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-46,39; 137,43</t>
+          <t>-44,89; 142,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34,72; 372,24</t>
+          <t>37,72; 353,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,0; 91,4</t>
+          <t>-47,02; 110,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28,98; 263,54</t>
+          <t>41,84; 287,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 77,88</t>
+          <t>-35,18; 67,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,21; 242,69</t>
+          <t>68,86; 257,5</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>2,83</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>2,97</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,46</t>
+          <t>-0,72; 0,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,76</t>
+          <t>2,38; 3,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,89</t>
+          <t>-0,54; 0,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,3</t>
+          <t>2,11; 3,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,43</t>
+          <t>-0,43; 0,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,41</t>
+          <t>2,4; 3,49</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>189,51%</t>
+          <t>201,88%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136,81%</t>
+          <t>152,53%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>160,23%</t>
+          <t>174,49%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-39,47; 36,29</t>
+          <t>-38,84; 44,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>97,18; 293,7</t>
+          <t>122,68; 321,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 58,11</t>
+          <t>-24,7; 52,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>72,18; 220,99</t>
+          <t>92,83; 231,4</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-23,73; 28,41</t>
+          <t>-22,76; 36,34</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>107,48; 230,77</t>
+          <t>118,05; 238,58</t>
         </is>
       </c>
     </row>
